--- a/docs/report/HIEX_intervention_metrics.xlsx
+++ b/docs/report/HIEX_intervention_metrics.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EP-validated ✓ </t>
+          <t xml:space="preserve">EP-checked — see Table 3 </t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">EP-validated ✓ </t>
+          <t xml:space="preserve">EP-checked — see Table 3 </t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">EP-validated ✓ </t>
+          <t xml:space="preserve">EP-checked — see Table 3 </t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">EP-validated ✓ </t>
+          <t xml:space="preserve">EP-checked — see Table 3 </t>
         </is>
       </c>
       <c r="R15" t="inlineStr">

--- a/docs/report/HIEX_intervention_metrics.xlsx
+++ b/docs/report/HIEX_intervention_metrics.xlsx
@@ -593,7 +593,7 @@
         <v>-3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>89.7</v>
+        <v>146.3</v>
       </c>
       <c r="O3" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="P3" t="n">
         <v>1.9</v>
@@ -737,10 +737,10 @@
         <v>-26</v>
       </c>
       <c r="N4" t="n">
-        <v>399.3</v>
+        <v>684.6</v>
       </c>
       <c r="O4" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -807,10 +807,10 @@
         <v>-8.5</v>
       </c>
       <c r="N5" t="n">
-        <v>83</v>
+        <v>135.4</v>
       </c>
       <c r="O5" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="P5" t="n">
         <v>5.4</v>
@@ -879,10 +879,10 @@
         <v>-3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>9.699999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="O6" t="n">
-        <v>268</v>
+        <v>543</v>
       </c>
       <c r="P6" t="n">
         <v>0.6</v>
@@ -951,10 +951,10 @@
         <v>-10.8</v>
       </c>
       <c r="N7" t="n">
-        <v>29.4</v>
+        <v>34.8</v>
       </c>
       <c r="O7" t="n">
-        <v>657</v>
+        <v>1332</v>
       </c>
       <c r="P7" t="n">
         <v>1.5</v>
@@ -1023,10 +1023,10 @@
         <v>-1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1338</v>
+        <v>2091</v>
       </c>
       <c r="P8" t="n">
         <v>3.4</v>
@@ -1045,12 +1045,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VRF metering, commissioning &amp; diagnostic health check</t>
+          <t>Fabric — glazing G-value (solar film)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Systems/controls</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1074,43 +1074,43 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8100</v>
+        <v>8685</v>
       </c>
       <c r="H9" t="n">
         <v>5000</v>
       </c>
       <c r="I9" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="J9" t="n">
-        <v>7233</v>
+        <v>4434</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2025</v>
+        <v>1242</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7</v>
+        <v>-1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1723</v>
+        <v>2554</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EP-validated ✓ </t>
+          <t xml:space="preserve">EP-checked — see Table 3 </t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Design note sensitivity band: none / central +0.4 / strong (managed 3.9). CENTRAL (+0.4 on in-service VRF heating SCOP + cooling EER, 3.0→3.4) is the stack member; none/strong stored as sensitivity. SAME PATH as 3.2 — 3.2 composes on the post-3.1 state.</t>
+          <t>Glazing g 0.55→0.42 (nearest library construction double_low_e; u unchanged at 1.4 — film reduces g, not u; doc target g 0.40). Expected marginal/counterproductive here (cuts useful winter heat, raises cooling). Film life ~10–15y in reality but note maps fabric→30y.</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         <v>14.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1736</v>
+        <v>2951</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
@@ -1242,7 +1242,7 @@
         <v>30.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1786</v>
+        <v>3036</v>
       </c>
       <c r="P11" t="n">
         <v>4.9</v>
@@ -1261,12 +1261,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fabric — glazing G-value (solar film)</t>
+          <t>VRF metering, commissioning &amp; diagnostic health check</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Systems/controls</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1290,43 +1290,43 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8685</v>
+        <v>8100</v>
       </c>
       <c r="H12" t="n">
         <v>5000</v>
       </c>
       <c r="I12" t="n">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="J12" t="n">
-        <v>4434</v>
+        <v>7233</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1242</v>
+        <v>2025</v>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2554</v>
+        <v>3535</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">EP-checked — see Table 3 </t>
+          <t xml:space="preserve">EP-validated ✓ </t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Glazing g 0.55→0.42 (nearest library construction double_low_e; u unchanged at 1.4 — film reduces g, not u; doc target g 0.40). Expected marginal/counterproductive here (cuts useful winter heat, raises cooling). Film life ~10–15y in reality but note maps fabric→30y.</t>
+          <t>Design note sensitivity band: none / central +0.4 / strong (managed 3.9). CENTRAL (+0.4 on in-service VRF heating SCOP + cooling EER, 3.0→3.4) is the stack member; none/strong stored as sensitivity. SAME PATH as 3.2 — 3.2 composes on the post-3.1 state.</t>
         </is>
       </c>
     </row>
@@ -1383,10 +1383,10 @@
         <v>-2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>79.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>4699</v>
+        <v>7909</v>
       </c>
       <c r="P13" t="n">
         <v>108.9</v>
@@ -1455,10 +1455,10 @@
         <v>-1.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>5025</v>
+        <v>7947</v>
       </c>
       <c r="P14" t="n">
         <v>12.6</v>
@@ -1599,7 +1599,7 @@
         <v>4.7</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.8</v>
+        <v>-15.1</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
